--- a/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4b/feature/swg45-add_chemotherapy_regimen/StructureDefinition-jp-practitioner.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1326,7 +1326,7 @@
   </si>
   <si>
     <t>使用のコンテキストは、範囲全体が適用されるか（例：「患者はこの時間範囲で病院の入院患者であった」）、範囲内の1つの値が適用されるか（例：「この2つの時間の間に患者に与える」）を指定する。  
-期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4/datatypes.html#Duration)を参照のこと。</t>
+期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration)を参照のこと。</t>
   </si>
   <si>
     <t>資格は期間限定のものが多く、取り消されることもある。</t>
